--- a/data/trans_dic/POLIPATOLOGIA_5-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_5-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas</t>
+          <t>Población con cinco o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,87; 8,91</t>
+          <t>5,86; 8,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,94; 12,01</t>
+          <t>7,88; 11,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,34; 11,3</t>
+          <t>7,43; 11,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,0; 25,29</t>
+          <t>19,32; 25,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,51; 15,03</t>
+          <t>11,29; 15,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,89; 22,5</t>
+          <t>17,85; 22,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,54; 24,19</t>
+          <t>18,45; 23,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,24; 40,79</t>
+          <t>35,06; 40,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,42; 11,84</t>
+          <t>9,35; 11,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,06; 17,32</t>
+          <t>14,31; 17,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,25; 18,0</t>
+          <t>14,34; 17,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,38; 33,7</t>
+          <t>29,47; 33,7</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,25</t>
+          <t>1,01; 2,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,04</t>
+          <t>0,98; 2,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,54</t>
+          <t>1,35; 2,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 6,98</t>
+          <t>4,09; 7,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,83</t>
+          <t>2,08; 3,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 4,92</t>
+          <t>2,98; 4,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,12</t>
+          <t>4,94; 7,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,39; 41,49</t>
+          <t>10,36; 38,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,72</t>
+          <t>1,7; 2,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,2</t>
+          <t>2,07; 3,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,48</t>
+          <t>3,24; 4,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 27,56</t>
+          <t>7,76; 26,78</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,61</t>
+          <t>1,11; 3,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,0</t>
+          <t>0,41; 3,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,79</t>
+          <t>0,93; 3,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,52</t>
+          <t>2,82; 5,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,36</t>
+          <t>0,78; 3,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,58</t>
+          <t>1,87; 5,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,05</t>
+          <t>1,84; 5,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,8; 10,44</t>
+          <t>6,85; 10,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,07</t>
+          <t>1,21; 2,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,78</t>
+          <t>1,42; 3,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,9</t>
+          <t>1,69; 3,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 7,33</t>
+          <t>5,2; 7,42</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,12</t>
+          <t>2,89; 4,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 4,55</t>
+          <t>3,15; 4,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 4,18</t>
+          <t>2,97; 4,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,07; 8,98</t>
+          <t>6,27; 8,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 7,71</t>
+          <t>5,91; 7,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,94; 11,03</t>
+          <t>8,89; 10,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,84; 10,95</t>
+          <t>8,77; 10,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,9; 35,92</t>
+          <t>15,93; 35,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 5,69</t>
+          <t>4,57; 5,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 7,58</t>
+          <t>6,29; 7,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,06; 7,38</t>
+          <t>6,12; 7,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,69; 23,59</t>
+          <t>11,62; 23,0</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas</t>
+          <t>Población con cinco o más enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>60586; 91876</t>
+          <t>60412; 91787</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>77395; 117024</t>
+          <t>76755; 116813</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55395; 85224</t>
+          <t>56073; 86744</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>97821; 130204</t>
+          <t>99466; 131247</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>151329; 197658</t>
+          <t>148484; 198498</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>239365; 301048</t>
+          <t>238740; 302142</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>184385; 240598</t>
+          <t>183515; 238319</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>266217; 308204</t>
+          <t>264902; 306231</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>220966; 277858</t>
+          <t>219334; 278627</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>325218; 400592</t>
+          <t>330948; 399717</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>249262; 314820</t>
+          <t>250807; 314254</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>373210; 428140</t>
+          <t>374408; 428171</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16760; 38121</t>
+          <t>17145; 38402</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19556; 39971</t>
+          <t>19256; 40408</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27828; 52820</t>
+          <t>28012; 52938</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90706; 159970</t>
+          <t>93607; 161031</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34606; 60791</t>
+          <t>33089; 61733</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51047; 86508</t>
+          <t>52390; 87120</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>97205; 141631</t>
+          <t>98175; 144202</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>232432; 928365</t>
+          <t>231864; 855414</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>55251; 89375</t>
+          <t>55700; 88988</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>76995; 119262</t>
+          <t>77009; 118137</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>132666; 182249</t>
+          <t>131849; 181872</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>355769; 1248129</t>
+          <t>351194; 1212740</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5943; 19925</t>
+          <t>6121; 20368</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1953; 14421</t>
+          <t>1951; 15295</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5585; 20718</t>
+          <t>5113; 19727</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17861; 35724</t>
+          <t>18252; 35897</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3992; 16004</t>
+          <t>3740; 15440</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9024; 25595</t>
+          <t>8595; 25436</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10024; 27730</t>
+          <t>10109; 27980</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>44919; 68920</t>
+          <t>45244; 69278</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11909; 31584</t>
+          <t>12391; 30527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13105; 35520</t>
+          <t>13317; 35148</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18599; 42762</t>
+          <t>18542; 42335</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>67097; 95821</t>
+          <t>67919; 96988</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>92695; 134837</t>
+          <t>94626; 136121</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>108066; 155514</t>
+          <t>107719; 154780</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98077; 141177</t>
+          <t>100279; 141374</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>209582; 309959</t>
+          <t>216377; 306954</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>198422; 260679</t>
+          <t>199560; 258014</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>317635; 392157</t>
+          <t>316033; 386592</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>312116; 386867</t>
+          <t>309929; 382325</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>581056; 1312265</t>
+          <t>581887; 1303859</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>306644; 378429</t>
+          <t>303891; 374096</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>437582; 528368</t>
+          <t>438847; 526698</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>418556; 509824</t>
+          <t>422567; 508806</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>830319; 1676120</t>
+          <t>825731; 1634296</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_5-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_5-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,9</t>
+          <t>5,8; 8,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,88; 11,99</t>
+          <t>8,03; 12,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 11,5</t>
+          <t>7,51; 11,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,32; 25,49</t>
+          <t>18,27; 24,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,29; 15,09</t>
+          <t>11,51; 15,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,85; 22,59</t>
+          <t>17,8; 22,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,45; 23,96</t>
+          <t>18,51; 24,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,06; 40,53</t>
+          <t>34,7; 39,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,35; 11,87</t>
+          <t>9,3; 11,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,31; 17,29</t>
+          <t>14,29; 17,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14,34; 17,97</t>
+          <t>14,26; 17,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,47; 33,7</t>
+          <t>28,54; 32,68</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,27</t>
+          <t>0,98; 2,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,06</t>
+          <t>0,95; 2,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,55</t>
+          <t>1,25; 2,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,03</t>
+          <t>5,61; 7,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,89</t>
+          <t>2,15; 3,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,96</t>
+          <t>2,91; 4,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 7,25</t>
+          <t>4,86; 7,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,36; 38,23</t>
+          <t>10,16; 12,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,71</t>
+          <t>1,74; 2,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,17</t>
+          <t>2,06; 3,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 4,47</t>
+          <t>3,24; 4,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,76; 26,78</t>
+          <t>8,15; 9,58</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,69</t>
+          <t>1,12; 3,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,18</t>
+          <t>0,41; 3,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,61</t>
+          <t>0,95; 3,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,55</t>
+          <t>2,79; 5,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,24</t>
+          <t>0,86; 3,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,55</t>
+          <t>1,95; 5,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,1</t>
+          <t>1,83; 5,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,85; 10,49</t>
+          <t>6,97; 10,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,97</t>
+          <t>1,2; 3,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,74</t>
+          <t>1,37; 3,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,86</t>
+          <t>1,58; 3,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 7,42</t>
+          <t>5,31; 7,57</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,15</t>
+          <t>2,82; 4,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,53</t>
+          <t>3,16; 4,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 4,19</t>
+          <t>3,04; 4,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 8,89</t>
+          <t>7,57; 9,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 7,64</t>
+          <t>5,89; 7,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,89; 10,88</t>
+          <t>8,88; 10,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 10,82</t>
+          <t>8,79; 10,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,93; 35,69</t>
+          <t>15,44; 17,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 5,62</t>
+          <t>4,56; 5,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,29; 7,55</t>
+          <t>6,27; 7,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 7,36</t>
+          <t>6,1; 7,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,62; 23,0</t>
+          <t>11,85; 13,19</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>113857</t>
+          <t>120945</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>286952</t>
+          <t>306519</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>400808</t>
+          <t>427463</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>60412; 91787</t>
+          <t>59812; 91850</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>76755; 116813</t>
+          <t>78228; 116992</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56073; 86744</t>
+          <t>56687; 85225</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99466; 131247</t>
+          <t>105711; 142543</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>148484; 198498</t>
+          <t>151364; 199749</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>238740; 302142</t>
+          <t>238176; 299509</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>183515; 238319</t>
+          <t>184091; 239867</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>264902; 306231</t>
+          <t>285277; 326852</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>219334; 278627</t>
+          <t>218259; 277089</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>330948; 399717</t>
+          <t>330445; 406958</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>250807; 314254</t>
+          <t>249381; 314128</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>374408; 428171</t>
+          <t>399697; 457750</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>134150</t>
+          <t>145337</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>424697</t>
+          <t>241879</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>558846</t>
+          <t>387216</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17145; 38402</t>
+          <t>16634; 37702</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19256; 40408</t>
+          <t>18570; 40107</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28012; 52938</t>
+          <t>25852; 52092</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93607; 161031</t>
+          <t>125144; 167725</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33089; 61733</t>
+          <t>34167; 62547</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52390; 87120</t>
+          <t>51071; 87003</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>98175; 144202</t>
+          <t>96543; 140376</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>231864; 855414</t>
+          <t>220554; 266225</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>55700; 88988</t>
+          <t>57240; 89539</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77009; 118137</t>
+          <t>76681; 116613</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>131849; 181872</t>
+          <t>131660; 183638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>351194; 1212740</t>
+          <t>358965; 421570</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26034</t>
+          <t>29074</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>55317</t>
+          <t>62645</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81350</t>
+          <t>91720</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6121; 20368</t>
+          <t>6198; 20856</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1951; 15295</t>
+          <t>1984; 18009</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5113; 19727</t>
+          <t>5212; 20459</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18252; 35897</t>
+          <t>19839; 40611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3740; 15440</t>
+          <t>4101; 16831</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8595; 25436</t>
+          <t>8932; 26028</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10109; 27980</t>
+          <t>10025; 29068</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45244; 69278</t>
+          <t>51191; 75917</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12391; 30527</t>
+          <t>12349; 30819</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13317; 35148</t>
+          <t>12829; 34583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18542; 42335</t>
+          <t>17322; 41222</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>67919; 96988</t>
+          <t>76739; 109466</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>274040</t>
+          <t>295356</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>766965</t>
+          <t>611043</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1041005</t>
+          <t>906399</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>94626; 136121</t>
+          <t>92334; 132324</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>107719; 154780</t>
+          <t>108022; 153204</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100279; 141374</t>
+          <t>102511; 142734</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>216377; 306954</t>
+          <t>266412; 329322</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>199560; 258014</t>
+          <t>198888; 259829</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>316033; 386592</t>
+          <t>315542; 388483</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>309929; 382325</t>
+          <t>310604; 388201</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>581887; 1303859</t>
+          <t>575568; 649216</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>303891; 374096</t>
+          <t>303623; 375812</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>438847; 526698</t>
+          <t>437388; 528045</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>422567; 508806</t>
+          <t>421702; 510001</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>825731; 1634296</t>
+          <t>859214; 955798</t>
         </is>
       </c>
     </row>
